--- a/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 3,41</t>
+          <t>-6,36; 3,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,51</t>
+          <t>-5,89; 7,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 9,57</t>
+          <t>-5,24; 9,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 4,9</t>
+          <t>-4,67; 4,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,47; 96,99</t>
+          <t>-77,56; 96,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,36; 167,64</t>
+          <t>-54,17; 172,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 175,41</t>
+          <t>-46,22; 180,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,7; 172,68</t>
+          <t>-69,61; 203,28</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 4,04</t>
+          <t>-6,54; 3,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 9,32</t>
+          <t>-2,34; 9,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,58</t>
+          <t>-2,24; 6,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 2,08</t>
+          <t>-6,85; 2,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,72; 70,63</t>
+          <t>-58,66; 72,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 169,94</t>
+          <t>-22,92; 170,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 186,41</t>
+          <t>-30,34; 197,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,17; 41,95</t>
+          <t>-66,72; 43,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 6,84</t>
+          <t>-3,97; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 8,78</t>
+          <t>-6,33; 9,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 8,84</t>
+          <t>-2,26; 9,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -0,05</t>
+          <t>-10,12; -0,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 228,84</t>
+          <t>-48,72; 201,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 90,45</t>
+          <t>-38,56; 98,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 191,01</t>
+          <t>-26,31; 222,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,02; 1,49</t>
+          <t>-76,73; -0,56</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 2,25</t>
+          <t>-8,57; 2,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 4,22</t>
+          <t>-6,9; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 5,66</t>
+          <t>-4,05; 5,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 2,96</t>
+          <t>-6,95; 3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 29,58</t>
+          <t>-64,42; 32,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,72; 80,72</t>
+          <t>-62,24; 61,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 142,93</t>
+          <t>-51,94; 142,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 49,39</t>
+          <t>-55,66; 58,5</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,18</t>
+          <t>-4,12; 1,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,0</t>
+          <t>-1,99; 4,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,42</t>
+          <t>-0,83; 4,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,18</t>
+          <t>-5,03; 0,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 18,0</t>
+          <t>-44,5; 18,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 52,1</t>
+          <t>-18,66; 54,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 81,97</t>
+          <t>-10,93; 86,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 5,05</t>
+          <t>-50,86; 5,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 3,44</t>
+          <t>-6,61; 3,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 7,7</t>
+          <t>-5,53; 7,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 9,47</t>
+          <t>-5,48; 9,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 4,86</t>
+          <t>-4,28; 4,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 96,12</t>
+          <t>-71,74; 99,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,17; 172,14</t>
+          <t>-57,7; 154,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 180,09</t>
+          <t>-46,43; 168,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,61; 203,28</t>
+          <t>-74,45; 186,14</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 3,73</t>
+          <t>-6,39; 4,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 9,01</t>
+          <t>-2,21; 9,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,82</t>
+          <t>-2,27; 6,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 2,19</t>
+          <t>-6,77; 1,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 72,72</t>
+          <t>-60,99; 77,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 170,53</t>
+          <t>-26,36; 161,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 197,8</t>
+          <t>-34,14; 181,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,72; 43,38</t>
+          <t>-64,31; 39,47</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 6,71</t>
+          <t>-3,78; 7,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 9,41</t>
+          <t>-6,64; 9,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 9,42</t>
+          <t>-2,0; 9,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,12; -0,2</t>
+          <t>-10,32; -0,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 201,4</t>
+          <t>-49,02; 219,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 98,12</t>
+          <t>-38,78; 89,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 222,41</t>
+          <t>-22,15; 199,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,73; -0,56</t>
+          <t>-76,45; 2,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 2,13</t>
+          <t>-8,89; 1,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,37</t>
+          <t>-6,89; 3,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,26</t>
+          <t>-3,9; 5,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 3,69</t>
+          <t>-7,01; 3,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,42; 32,46</t>
+          <t>-64,36; 20,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 61,64</t>
+          <t>-62,46; 66,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 142,28</t>
+          <t>-50,59; 142,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 58,5</t>
+          <t>-55,56; 54,77</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,23</t>
+          <t>-3,99; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,26</t>
+          <t>-1,8; 4,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,66</t>
+          <t>-0,79; 4,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,28</t>
+          <t>-4,63; 0,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 18,72</t>
+          <t>-43,1; 19,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 54,7</t>
+          <t>-17,64; 56,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 86,24</t>
+          <t>-9,91; 88,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 5,59</t>
+          <t>-49,08; 5,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 3,05</t>
+          <t>-6,45; 3,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 7,73</t>
+          <t>-5,02; 7,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 9,2</t>
+          <t>-5,23; 9,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 4,84</t>
+          <t>-4,24; 5,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,74; 99,89</t>
+          <t>-74,47; 96,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 154,64</t>
+          <t>-53,36; 167,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 168,09</t>
+          <t>-46,95; 175,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,45; 186,14</t>
+          <t>-68,18; 196,02</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-26,2%</t>
+          <t>-29,38%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 4,0</t>
+          <t>-6,36; 4,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 9,67</t>
+          <t>-2,26; 9,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 6,38</t>
+          <t>-2,19; 6,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,81</t>
+          <t>-7,25; 1,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 77,3</t>
+          <t>-60,72; 70,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 161,43</t>
+          <t>-25,36; 169,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 181,11</t>
+          <t>-32,12; 186,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 39,47</t>
+          <t>-65,63; 33,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,87</t>
+          <t>-3,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-47,48%</t>
+          <t>-32,32%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 7,13</t>
+          <t>-3,61; 6,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 9,06</t>
+          <t>-5,71; 8,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 9,92</t>
+          <t>-2,85; 8,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -0,05</t>
+          <t>-8,0; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 219,35</t>
+          <t>-45,75; 228,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 89,61</t>
+          <t>-37,0; 90,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 199,35</t>
+          <t>-29,18; 191,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,45; 2,67</t>
+          <t>-64,29; 31,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-16,8%</t>
+          <t>-7,53%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 1,39</t>
+          <t>-8,39; 2,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 3,63</t>
+          <t>-6,71; 4,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 5,3</t>
+          <t>-3,86; 5,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,55</t>
+          <t>-5,63; 4,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,36; 20,35</t>
+          <t>-64,55; 29,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,46; 66,36</t>
+          <t>-59,72; 80,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 142,78</t>
+          <t>-49,45; 142,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,56; 54,77</t>
+          <t>-46,76; 67,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-26,86%</t>
+          <t>-19,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,22</t>
+          <t>-3,97; 1,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,17</t>
+          <t>-2,11; 4,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,68</t>
+          <t>-0,73; 4,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,45</t>
+          <t>-4,02; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 19,28</t>
+          <t>-42,67; 18,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 56,1</t>
+          <t>-19,37; 52,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 88,26</t>
+          <t>-9,69; 81,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 5,79</t>
+          <t>-43,09; 14,84</t>
         </is>
       </c>
     </row>
